--- a/output/pdf_financials_xlsx/QGR.xlsx
+++ b/output/pdf_financials_xlsx/QGR.xlsx
@@ -6202,28 +6202,28 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.11978</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.9974499999999999</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.030238</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.030238</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.030238</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.030238</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.030238</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.030238</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -6238,13 +6238,13 @@
         <v>0</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.216327</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.409735</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>6.360984</v>
       </c>
     </row>
     <row r="93">
@@ -10547,7 +10547,11 @@
           <t>Warrants reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10646,7 +10650,11 @@
           <t>Share based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -16693,7 +16701,11 @@
           <t>Reserve for warrants (Note 8)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -18511,7 +18523,11 @@
           <t>Reserve for warrants (Note 8) 1,030,238</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -20454,7 +20470,11 @@
           <t>Reserve for warrants (Note 8) 1,030,238</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -21868,7 +21888,11 @@
           <t>Reserve for warrants (Note 9)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -23496,7 +23520,11 @@
           <t>Reserve for warrants (Note 9) 997,450</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/QGR.xlsx
+++ b/output/pdf_financials_xlsx/QGR.xlsx
@@ -972,28 +972,28 @@
         <v>0.555315</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.494592</v>
+        <v>0.478285</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.13949</v>
+        <v>0.592709</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.00963</v>
+        <v>0.549637</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.004444</v>
+        <v>2.330074</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.009941</v>
+        <v>1.742609</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.209496</v>
+        <v>0.490744</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.214855</v>
+        <v>0.39077</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>1.677321</v>
+        <v>22.182319</v>
       </c>
     </row>
     <row r="11">
@@ -1037,25 +1037,25 @@
         <v>-0.494592</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.13949</v>
+        <v>-0.592709</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.00963</v>
+        <v>-0.549637</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.004444</v>
+        <v>-2.330074</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.009941</v>
+        <v>-1.742609</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.209496</v>
+        <v>-0.490744</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.214855</v>
+        <v>-0.39077</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-1.677321</v>
+        <v>-22.182319</v>
       </c>
     </row>
     <row r="12">
@@ -1075,40 +1075,40 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001964</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001481</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000207</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>3.3e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>4.2e-05</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>3.6e-05</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000309</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.003427</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.020556</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -1117,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.008829999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2093,40 +2093,40 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.017549</v>
+        <v>-2.019513</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.964833</v>
+        <v>-1.966314</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.942231</v>
+        <v>-0.942438</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.351812</v>
+        <v>-0.351816</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.261452</v>
+        <v>-0.261485</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.195572</v>
+        <v>-0.195614</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.555279</v>
+        <v>-0.555315</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.366232</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.593734</v>
+        <v>-0.594043</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.547757</v>
+        <v>-0.551184</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.321373</v>
+        <v>-2.341929</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.973034</v>
+        <v>-2.003034</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.612003</v>
@@ -2135,7 +2135,7 @@
         <v>-0.439688</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-22.235079</v>
+        <v>-22.243909</v>
       </c>
     </row>
     <row r="28">
@@ -2217,40 +2217,40 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.017549</v>
+        <v>-2.019513</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.964833</v>
+        <v>-1.966314</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.942231</v>
+        <v>-0.942438</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.351812</v>
+        <v>-0.351816</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.261452</v>
+        <v>-0.261485</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.195572</v>
+        <v>-0.195614</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.555279</v>
+        <v>-0.555315</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.366232</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.593734</v>
+        <v>-0.594043</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.547757</v>
+        <v>-0.551184</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.321373</v>
+        <v>-2.341929</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.973034</v>
+        <v>-2.003034</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.612003</v>
@@ -2259,7 +2259,7 @@
         <v>-0.439688</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-22.235079</v>
+        <v>-22.243909</v>
       </c>
     </row>
     <row r="30">
@@ -2279,25 +2279,25 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-19656.55689789556</v>
+        <v>-19675.69173811379</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-9240.61985608804</v>
+        <v>-9247.585006819358</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-1046.016785452608</v>
+        <v>-1046.24658629188</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-8795300</v>
+        <v>-8795400</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-792278.7878787878</v>
+        <v>-792378.7878787878</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-465647.6190476191</v>
+        <v>-465747.6190476191</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1542441.666666667</v>
+        <v>-1542541.666666667</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -2525,28 +2525,28 @@
         <v>0.004477</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.000411</v>
+        <v>0.001469</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.454734</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.068069</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.044566</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.237436</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.010476</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.718716</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>4.665022</v>
       </c>
     </row>
     <row r="35">
@@ -2649,28 +2649,28 @@
         <v>0.004477</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.000411</v>
+        <v>0.001469</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.454734</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.068069</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.044566</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.237436</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.010476</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.718716</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>4.665022</v>
       </c>
     </row>
     <row r="37">
@@ -3393,28 +3393,28 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.001058</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.460792</v>
+        <v>0.006058</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.068069</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.07125099999999999</v>
+        <v>0.026685</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.254554</v>
+        <v>0.017118</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.015359</v>
+        <v>0.004883</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.720622</v>
+        <v>0.001906</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>5.360288</v>
+        <v>0.6952660000000001</v>
       </c>
     </row>
     <row r="49">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -34132,7 +34132,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -34629,7 +34629,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -38106,7 +38106,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -40217,7 +40217,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -41124,7 +41124,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -41229,7 +41229,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -41742,7 +41742,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -44421,7 +44421,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">

--- a/output/pdf_financials_xlsx/QGR.xlsx
+++ b/output/pdf_financials_xlsx/QGR.xlsx
@@ -42140,7 +42140,11 @@
           <t>Amortization Note 6 704</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/QGR.xlsx
+++ b/output/pdf_financials_xlsx/QGR.xlsx
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.144943</v>
+        <v>0.180943</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.153978</v>
+        <v>0.156765</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.149676</v>
@@ -786,28 +786,28 @@
         <v>0.014312</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.005109</v>
+        <v>0.013797</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.13949</v>
+        <v>0.149009</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.00963</v>
+        <v>0.09075</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.004444</v>
+        <v>0.09257799999999999</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.009941</v>
+        <v>0.089587</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.209496</v>
+        <v>0.285892</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.214855</v>
+        <v>0.282771</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>1.677321</v>
+        <v>1.802273</v>
       </c>
     </row>
     <row r="8">
@@ -7071,16 +7071,16 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>0.134631</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>0.321649</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>0.199896</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>0.042317</v>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
@@ -7088,10 +7088,10 @@
         </is>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>0.08587</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>0.028372</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>0.088246</v>
@@ -7650,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.0165</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -31325,7 +31325,11 @@
           <t>Changes in non-cash operating working capital (Note 11)</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -32580,7 +32584,11 @@
           <t>Changes in non-cash operating working capital (Note 12)</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -32677,7 +32685,11 @@
           <t>Proceeds from sale of marketable securities (Note 5)</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -33673,7 +33685,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -49448,7 +49464,11 @@
           <t>Directors fees (Note 4)</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
